--- a/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
+++ b/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9463113F-022E-46A7-8F7E-E10F1A1436E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAABD293-9367-4510-B3F2-DD5951F69DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
+    <workbookView xWindow="14303" yWindow="2595" windowWidth="21795" windowHeight="12975" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,10 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Order Number</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>Type</t>
   </si>
@@ -53,13 +50,73 @@
   </si>
   <si>
     <t>Full Scannable Order Number</t>
+  </si>
+  <si>
+    <t>Type Options</t>
+  </si>
+  <si>
+    <t>VPD</t>
+  </si>
+  <si>
+    <t>VPD Transom</t>
+  </si>
+  <si>
+    <t>VPD FrameOnly</t>
+  </si>
+  <si>
+    <t>VPD ActivePanelOnly</t>
+  </si>
+  <si>
+    <t>VPD InactivePanelOnly</t>
+  </si>
+  <si>
+    <t>R-SO-5114589-1.001-1</t>
+  </si>
+  <si>
+    <t>R-SO-5106483-1-1</t>
+  </si>
+  <si>
+    <t>Amaya</t>
+  </si>
+  <si>
+    <t>Rebs</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>Cville</t>
+  </si>
+  <si>
+    <t>Colour Options</t>
+  </si>
+  <si>
+    <t>White/White</t>
+  </si>
+  <si>
+    <t>Clay/Clay</t>
+  </si>
+  <si>
+    <t>Almond/Almond</t>
+  </si>
+  <si>
+    <t>Bronze/White</t>
+  </si>
+  <si>
+    <t>Bronze/Bronze</t>
+  </si>
+  <si>
+    <t>Black/White</t>
+  </si>
+  <si>
+    <t>Black/Black</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,6 +134,14 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,10 +177,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,65 +497,189 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0080E7-F391-47B1-85B3-22F42F81BBBC}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
     <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>71.5</v>
+      </c>
+      <c r="D2">
+        <v>79.5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46091</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>71.5</v>
+      </c>
+      <c r="D3">
+        <v>95.5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46091</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Exceeded character length" error="Order number needs to be 10 characters or less" sqref="A1" xr:uid="{7C21A31A-C1BB-4D92-B294-FB94B161F595}">
-      <formula1>0</formula1>
-      <formula2>10</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9744BA83-CC56-4834-8B3C-78067D3AFEDF}">
+          <x14:formula1>
+            <xm:f>Sheet2!$B$4:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>B1:B1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FC21A485-6620-4D2F-9802-6D8F49E5F33E}">
+          <x14:formula1>
+            <xm:f>Sheet2!$E$4:$E$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>E1:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1C98EE-729B-49CB-B4CB-083EAD0CF0A0}">
-  <dimension ref="A1"/>
+  <dimension ref="B3:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
+++ b/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAABD293-9367-4510-B3F2-DD5951F69DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99DA321-4198-43EE-BEBE-E07807382B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="2595" windowWidth="21795" windowHeight="12975" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>Type</t>
   </si>
@@ -70,19 +70,10 @@
     <t>VPD InactivePanelOnly</t>
   </si>
   <si>
-    <t>R-SO-5114589-1.001-1</t>
-  </si>
-  <si>
     <t>R-SO-5106483-1-1</t>
   </si>
   <si>
-    <t>Amaya</t>
-  </si>
-  <si>
     <t>Rebs</t>
-  </si>
-  <si>
-    <t>Dallas</t>
   </si>
   <si>
     <t>Cville</t>
@@ -546,24 +537,24 @@
         <v>71.5</v>
       </c>
       <c r="D2">
-        <v>79.5</v>
+        <v>95.5</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4">
         <v>46091</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -575,16 +566,16 @@
         <v>95.5</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G3" s="4">
         <v>46091</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +616,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -633,7 +624,7 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -641,7 +632,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
@@ -649,7 +640,7 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -657,7 +648,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -665,17 +656,17 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
+++ b/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99DA321-4198-43EE-BEBE-E07807382B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC1522F-3E4A-4485-BA21-F159EB7D1E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
+    <workbookView xWindow="-3195" yWindow="2760" windowWidth="21585" windowHeight="12765" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Type</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Black/Black</t>
+  </si>
+  <si>
+    <t>R-SO-5106483-1-2</t>
   </si>
 </sst>
 </file>
@@ -492,6 +495,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" customWidth="1"/>
@@ -554,7 +558,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>

--- a/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
+++ b/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC1522F-3E4A-4485-BA21-F159EB7D1E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22ACB638-831E-40B7-91A4-4CAFBD89C91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3195" yWindow="2760" windowWidth="21585" windowHeight="12765" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
+    <workbookView xWindow="-16275" yWindow="4635" windowWidth="14040" windowHeight="9375" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
   <si>
     <t>Type</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>R-SO-5106483-1-2</t>
+  </si>
+  <si>
+    <t>R-SO-5106483-1-3</t>
   </si>
 </sst>
 </file>
@@ -491,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0080E7-F391-47B1-85B3-22F42F81BBBC}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -579,6 +582,32 @@
         <v>46091</v>
       </c>
       <c r="H3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>71.5</v>
+      </c>
+      <c r="D4">
+        <v>95.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46091</v>
+      </c>
+      <c r="H4" t="s">
         <v>16</v>
       </c>
     </row>

--- a/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
+++ b/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22ACB638-831E-40B7-91A4-4CAFBD89C91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A38BDBB-0076-43BA-88A9-B23A79E05E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16275" yWindow="4635" windowWidth="14040" windowHeight="9375" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
   <si>
     <t>Type</t>
   </si>
@@ -70,9 +70,6 @@
     <t>VPD InactivePanelOnly</t>
   </si>
   <si>
-    <t>R-SO-5106483-1-1</t>
-  </si>
-  <si>
     <t>Rebs</t>
   </si>
   <si>
@@ -103,17 +100,32 @@
     <t>Black/Black</t>
   </si>
   <si>
-    <t>R-SO-5106483-1-2</t>
-  </si>
-  <si>
-    <t>R-SO-5106483-1-3</t>
+    <t>R-SO-5088990-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-2</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-2-1</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-2-2</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-3-1</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-4-1</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-4-2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +152,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -494,14 +512,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0080E7-F391-47B1-85B3-22F42F81BBBC}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
@@ -535,7 +553,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -544,19 +562,19 @@
         <v>71.5</v>
       </c>
       <c r="D2">
-        <v>95.5</v>
+        <v>79.5</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H2" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" s="4">
-        <v>46091</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -570,19 +588,19 @@
         <v>71.5</v>
       </c>
       <c r="D3">
-        <v>95.5</v>
+        <v>79.5</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H3" t="s">
         <v>15</v>
-      </c>
-      <c r="G3" s="4">
-        <v>46091</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -596,22 +614,127 @@
         <v>71.5</v>
       </c>
       <c r="D4">
-        <v>95.5</v>
+        <v>79.5</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="4">
-        <v>46091</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>71.5</v>
+      </c>
+      <c r="D5">
+        <v>79.5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>71.5</v>
+      </c>
+      <c r="D6">
+        <v>79.5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>59.5</v>
+      </c>
+      <c r="D7">
+        <v>79.5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>59.5</v>
+      </c>
+      <c r="D8">
+        <v>79.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
@@ -649,7 +772,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -657,7 +780,7 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -665,7 +788,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
@@ -673,7 +796,7 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -681,7 +804,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -689,17 +812,17 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
+++ b/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A38BDBB-0076-43BA-88A9-B23A79E05E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BFD1A9-D6E7-4873-B140-1A2C18555C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
+    <workbookView xWindow="14303" yWindow="2595" windowWidth="21795" windowHeight="12975" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -106,19 +106,19 @@
     <t>R-SO-5088990-1-2</t>
   </si>
   <si>
-    <t>R-SO-5088990-2-1</t>
-  </si>
-  <si>
-    <t>R-SO-5088990-2-2</t>
-  </si>
-  <si>
-    <t>R-SO-5088990-3-1</t>
-  </si>
-  <si>
-    <t>R-SO-5088990-4-1</t>
-  </si>
-  <si>
-    <t>R-SO-5088990-4-2</t>
+    <t>R-SO-5088990-1-3</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-4</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-5</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-6</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-7</t>
   </si>
 </sst>
 </file>

--- a/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
+++ b/VPD PO download generator/VPD PO Download Spreadsheet V0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BFD1A9-D6E7-4873-B140-1A2C18555C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910116DF-DD79-4D18-8522-40D29A76DFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14303" yWindow="2595" windowWidth="21795" windowHeight="12975" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
   <si>
     <t>Type</t>
   </si>
@@ -119,6 +119,30 @@
   </si>
   <si>
     <t>R-SO-5088990-1-7</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-11</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-12</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-13</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-14</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-15</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-16</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-17</t>
+  </si>
+  <si>
+    <t>R-SO-5088990-1-18</t>
   </si>
 </sst>
 </file>
@@ -512,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0080E7-F391-47B1-85B3-22F42F81BBBC}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -730,6 +754,214 @@
         <v>46007</v>
       </c>
       <c r="H8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>71.5</v>
+      </c>
+      <c r="D9">
+        <v>79.5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>71.5</v>
+      </c>
+      <c r="D10">
+        <v>79.5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>71.5</v>
+      </c>
+      <c r="D11">
+        <v>79.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>71.5</v>
+      </c>
+      <c r="D12">
+        <v>79.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>71.5</v>
+      </c>
+      <c r="D13">
+        <v>79.5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>59.5</v>
+      </c>
+      <c r="D14">
+        <v>79.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>59.5</v>
+      </c>
+      <c r="D15">
+        <v>79.5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>59.5</v>
+      </c>
+      <c r="D16">
+        <v>79.5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46008</v>
+      </c>
+      <c r="H16" t="s">
         <v>15</v>
       </c>
     </row>
